--- a/data/facies.xlsx
+++ b/data/facies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbo062\src\darsia-projects\ff_glass_beads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27280DBE-4DC0-4416-957F-AF89E2D62D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B213E8-7D4F-4D17-8D91-2709D346B590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{80B7790F-1F10-4EF0-9A86-CCBE64830FC7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>name</t>
   </si>
@@ -456,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A962DD-BB00-44DA-994E-C6955E5BDA5D}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -662,6 +662,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>0.4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
